--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4924-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4924-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4704A7-772E-46B1-9DCA-16893FF955AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{043A3548-FF88-48EB-A29D-05F9010FE24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{AB4AA613-E0E0-428D-B60A-A51009BC795A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{19B3ACC2-14DD-4206-8908-C5653B162B84}"/>
   </bookViews>
   <sheets>
     <sheet name="4924-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1460,24 +1460,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36D6C51B-41AC-455C-8B7F-969EDBA0C6EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003B8612-EC17-425F-A77B-B18FD777EE43}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.77734375" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="10.125" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="9" width="10.125" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="13" width="10.125" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1631,7 +1631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2018</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2017</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2016</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2015</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2014</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2013</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2012</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2011</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2010</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
         <v>39</v>
       </c>
